--- a/Liga 2021-22/cromos_laliga.xlsx
+++ b/Liga 2021-22/cromos_laliga.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Documents\Cromos\Liga 2021-22\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuari\Documents\Cromos\Liga 2021-22\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3503EBF-9376-45E3-9A99-6274468E59C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41AE1BD-DBD5-4171-AA6A-B92EF4B74B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -4391,7 +4391,7 @@
     <xf numFmtId="0" fontId="3" fillId="37" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -4413,9 +4413,6 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4435,6 +4432,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4752,9 +4752,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.33203125" customWidth="1"/>
+    <col min="1" max="1" width="38.28515625" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
@@ -4763,7 +4763,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
         <v>58</v>
       </c>
@@ -4771,7 +4771,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>59</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>63</v>
       </c>
@@ -4822,7 +4822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>64</v>
       </c>
@@ -4850,7 +4850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>65</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>66</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>67</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>68</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>69</v>
       </c>
@@ -4990,7 +4990,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>70</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>71</v>
       </c>
@@ -5039,14 +5039,14 @@
       </c>
       <c r="F11" s="28">
         <f>SUM('RCD ESPANYOL'!F3:F26)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" s="33">
         <f>SUM('RCD ESPANYOL'!G3:G26)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>72</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>73</v>
       </c>
@@ -5102,7 +5102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>74</v>
       </c>
@@ -5123,14 +5123,14 @@
       </c>
       <c r="F14" s="28">
         <f>SUM('LEVANTE UD'!F3:F27)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G14" s="33">
         <f>SUM('LEVANTE UD'!G3:G27)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>75</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>76</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>77</v>
       </c>
@@ -5214,7 +5214,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>78</v>
       </c>
@@ -5242,7 +5242,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>79</v>
       </c>
@@ -5270,7 +5270,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>80</v>
       </c>
@@ -5291,14 +5291,14 @@
       </c>
       <c r="F20" s="28">
         <f>SUM('SEVILLA FC'!F3:F26)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20" s="33">
         <f>SUM('SEVILLA FC'!G3:G26)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>0</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>81</v>
       </c>
@@ -5354,7 +5354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>82</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>83</v>
       </c>
@@ -5410,7 +5410,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>84</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>85</v>
       </c>
@@ -5466,7 +5466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>86</v>
       </c>
@@ -5488,20 +5488,20 @@
       </c>
       <c r="F27" s="30">
         <f t="shared" si="0"/>
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G27" s="34">
         <f t="shared" si="0"/>
-        <v>141</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="37"/>
       <c r="B28" s="37"/>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>87</v>
       </c>
@@ -5518,7 +5518,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -5528,15 +5528,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
         <v>70</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5559,7 +5559,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>493</v>
       </c>
@@ -5577,7 +5577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>495</v>
       </c>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>497</v>
       </c>
@@ -5617,7 +5617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>499</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>501</v>
       </c>
@@ -5653,7 +5653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>502</v>
       </c>
@@ -5673,7 +5673,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>504</v>
       </c>
@@ -5691,7 +5691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>506</v>
       </c>
@@ -5709,7 +5709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>508</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>510</v>
       </c>
@@ -5749,7 +5749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>512</v>
       </c>
@@ -5767,7 +5767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>514</v>
       </c>
@@ -5789,7 +5789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>516</v>
       </c>
@@ -5811,7 +5811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>518</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>520</v>
       </c>
@@ -5847,7 +5847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>522</v>
       </c>
@@ -5865,7 +5865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>524</v>
       </c>
@@ -5885,7 +5885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>525</v>
       </c>
@@ -5907,7 +5907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>526</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>528</v>
       </c>
@@ -5943,7 +5943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>530</v>
       </c>
@@ -5965,7 +5965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>532</v>
       </c>
@@ -5981,7 +5981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>534</v>
       </c>
@@ -5999,7 +5999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>536</v>
       </c>
@@ -6017,7 +6017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>538</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>540</v>
       </c>
@@ -6066,7 +6066,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -6076,15 +6076,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -6107,7 +6107,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>542</v>
       </c>
@@ -6127,7 +6127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>544</v>
       </c>
@@ -6149,7 +6149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>546</v>
       </c>
@@ -6171,7 +6171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>547</v>
       </c>
@@ -6189,7 +6189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>549</v>
       </c>
@@ -6211,7 +6211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>551</v>
       </c>
@@ -6229,7 +6229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>553</v>
       </c>
@@ -6251,7 +6251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>555</v>
       </c>
@@ -6269,7 +6269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>557</v>
       </c>
@@ -6291,7 +6291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>559</v>
       </c>
@@ -6306,14 +6306,14 @@
         <v>2</v>
       </c>
       <c r="F12" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>561</v>
       </c>
@@ -6331,7 +6331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>563</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>565</v>
       </c>
@@ -6369,7 +6369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>567</v>
       </c>
@@ -6389,7 +6389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>569</v>
       </c>
@@ -6409,7 +6409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>571</v>
       </c>
@@ -6427,7 +6427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>573</v>
       </c>
@@ -6447,7 +6447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>575</v>
       </c>
@@ -6465,7 +6465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>577</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>579</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>580</v>
       </c>
@@ -6527,7 +6527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>582</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>584</v>
       </c>
@@ -6565,7 +6565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>585</v>
       </c>
@@ -6594,7 +6594,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -6604,15 +6604,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
         <v>72</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>587</v>
       </c>
@@ -6653,7 +6653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>589</v>
       </c>
@@ -6673,7 +6673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>591</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>592</v>
       </c>
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>594</v>
       </c>
@@ -6729,7 +6729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>596</v>
       </c>
@@ -6749,7 +6749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>598</v>
       </c>
@@ -6771,7 +6771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>600</v>
       </c>
@@ -6787,7 +6787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>602</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>604</v>
       </c>
@@ -6827,7 +6827,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>606</v>
       </c>
@@ -6845,7 +6845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>608</v>
       </c>
@@ -6867,7 +6867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>610</v>
       </c>
@@ -6887,7 +6887,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>612</v>
       </c>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>614</v>
       </c>
@@ -6921,7 +6921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>616</v>
       </c>
@@ -6937,7 +6937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>617</v>
       </c>
@@ -6957,7 +6957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>618</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>620</v>
       </c>
@@ -6997,7 +6997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>622</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>624</v>
       </c>
@@ -7033,7 +7033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>626</v>
       </c>
@@ -7051,7 +7051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>628</v>
       </c>
@@ -7069,7 +7069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>630</v>
       </c>
@@ -7087,7 +7087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>632</v>
       </c>
@@ -7109,7 +7109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>634</v>
       </c>
@@ -7129,7 +7129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>636</v>
       </c>
@@ -7145,7 +7145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>638</v>
       </c>
@@ -7174,7 +7174,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -7184,7 +7184,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="41" t="s">
         <v>73</v>
       </c>
@@ -7192,7 +7192,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>640</v>
       </c>
@@ -7237,7 +7237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>642</v>
       </c>
@@ -7255,7 +7255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>644</v>
       </c>
@@ -7273,7 +7273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>646</v>
       </c>
@@ -7295,7 +7295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>648</v>
       </c>
@@ -7313,7 +7313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>650</v>
       </c>
@@ -7333,7 +7333,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>652</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>654</v>
       </c>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>656</v>
       </c>
@@ -7391,7 +7391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>658</v>
       </c>
@@ -7409,7 +7409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>660</v>
       </c>
@@ -7429,7 +7429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>662</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>664</v>
       </c>
@@ -7471,7 +7471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>666</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>668</v>
       </c>
@@ -7507,7 +7507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>670</v>
       </c>
@@ -7525,7 +7525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>672</v>
       </c>
@@ -7543,7 +7543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>674</v>
       </c>
@@ -7561,7 +7561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>676</v>
       </c>
@@ -7579,7 +7579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>677</v>
       </c>
@@ -7597,7 +7597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>679</v>
       </c>
@@ -7617,7 +7617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>681</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>682</v>
       </c>
@@ -7651,7 +7651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>684</v>
       </c>
@@ -7680,7 +7680,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -7690,15 +7690,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="48" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -7721,7 +7721,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>686</v>
       </c>
@@ -7741,7 +7741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>688</v>
       </c>
@@ -7759,7 +7759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>690</v>
       </c>
@@ -7773,13 +7773,15 @@
       <c r="E5" s="14">
         <v>1</v>
       </c>
-      <c r="F5" s="31"/>
+      <c r="F5" s="31">
+        <v>1</v>
+      </c>
       <c r="G5" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>692</v>
       </c>
@@ -7801,7 +7803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>694</v>
       </c>
@@ -7823,7 +7825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>696</v>
       </c>
@@ -7845,7 +7847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>697</v>
       </c>
@@ -7863,7 +7865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>699</v>
       </c>
@@ -7879,7 +7881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>701</v>
       </c>
@@ -7897,7 +7899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>703</v>
       </c>
@@ -7919,7 +7921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>705</v>
       </c>
@@ -7939,7 +7941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>707</v>
       </c>
@@ -7955,7 +7957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>709</v>
       </c>
@@ -7975,7 +7977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>711</v>
       </c>
@@ -7991,7 +7993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>713</v>
       </c>
@@ -8009,7 +8011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>715</v>
       </c>
@@ -8027,7 +8029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>717</v>
       </c>
@@ -8049,7 +8051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>718</v>
       </c>
@@ -8069,7 +8071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>720</v>
       </c>
@@ -8091,7 +8093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>722</v>
       </c>
@@ -8109,7 +8111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>724</v>
       </c>
@@ -8129,7 +8131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>726</v>
       </c>
@@ -8147,7 +8149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>728</v>
       </c>
@@ -8165,7 +8167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>729</v>
       </c>
@@ -8181,7 +8183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>731</v>
       </c>
@@ -8208,7 +8210,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -8218,15 +8220,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="49" t="s">
         <v>75</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -8249,7 +8251,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>733</v>
       </c>
@@ -8267,7 +8269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>735</v>
       </c>
@@ -8289,7 +8291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>737</v>
       </c>
@@ -8307,7 +8309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>738</v>
       </c>
@@ -8325,7 +8327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>740</v>
       </c>
@@ -8343,7 +8345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>742</v>
       </c>
@@ -8365,7 +8367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>744</v>
       </c>
@@ -8383,7 +8385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>746</v>
       </c>
@@ -8403,7 +8405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>748</v>
       </c>
@@ -8421,7 +8423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>750</v>
       </c>
@@ -8437,7 +8439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>752</v>
       </c>
@@ -8455,7 +8457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>754</v>
       </c>
@@ -8475,7 +8477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>756</v>
       </c>
@@ -8497,7 +8499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>758</v>
       </c>
@@ -8519,7 +8521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>760</v>
       </c>
@@ -8541,7 +8543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>762</v>
       </c>
@@ -8563,7 +8565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>764</v>
       </c>
@@ -8585,7 +8587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>766</v>
       </c>
@@ -8605,7 +8607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>768</v>
       </c>
@@ -8627,7 +8629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>770</v>
       </c>
@@ -8643,7 +8645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>772</v>
       </c>
@@ -8659,7 +8661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>774</v>
       </c>
@@ -8677,7 +8679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>776</v>
       </c>
@@ -8695,7 +8697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>777</v>
       </c>
@@ -8713,7 +8715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>778</v>
       </c>
@@ -8731,7 +8733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>780</v>
       </c>
@@ -8747,7 +8749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>782</v>
       </c>
@@ -8776,7 +8778,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -8786,7 +8788,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="41" t="s">
         <v>76</v>
       </c>
@@ -8794,7 +8796,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -8817,7 +8819,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>784</v>
       </c>
@@ -8835,7 +8837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>786</v>
       </c>
@@ -8853,7 +8855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>788</v>
       </c>
@@ -8871,7 +8873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>790</v>
       </c>
@@ -8893,7 +8895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>792</v>
       </c>
@@ -8911,7 +8913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>794</v>
       </c>
@@ -8929,7 +8931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>796</v>
       </c>
@@ -8947,7 +8949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>798</v>
       </c>
@@ -8965,7 +8967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>800</v>
       </c>
@@ -8987,7 +8989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>802</v>
       </c>
@@ -9005,7 +9007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>804</v>
       </c>
@@ -9021,7 +9023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>806</v>
       </c>
@@ -9039,7 +9041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>808</v>
       </c>
@@ -9055,7 +9057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>810</v>
       </c>
@@ -9073,7 +9075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>812</v>
       </c>
@@ -9093,7 +9095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>814</v>
       </c>
@@ -9109,7 +9111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>816</v>
       </c>
@@ -9127,7 +9129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>817</v>
       </c>
@@ -9145,7 +9147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>819</v>
       </c>
@@ -9167,7 +9169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>821</v>
       </c>
@@ -9189,7 +9191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>823</v>
       </c>
@@ -9205,7 +9207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>825</v>
       </c>
@@ -9223,7 +9225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>826</v>
       </c>
@@ -9241,7 +9243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>828</v>
       </c>
@@ -9259,7 +9261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>830</v>
       </c>
@@ -9288,7 +9290,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -9298,7 +9300,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="41" t="s">
         <v>77</v>
       </c>
@@ -9306,7 +9308,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9329,7 +9331,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>832</v>
       </c>
@@ -9349,7 +9351,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>834</v>
       </c>
@@ -9367,7 +9369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>836</v>
       </c>
@@ -9387,7 +9389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>837</v>
       </c>
@@ -9409,7 +9411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>839</v>
       </c>
@@ -9429,7 +9431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>841</v>
       </c>
@@ -9447,7 +9449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>843</v>
       </c>
@@ -9467,7 +9469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>845</v>
       </c>
@@ -9483,7 +9485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>847</v>
       </c>
@@ -9501,7 +9503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>849</v>
       </c>
@@ -9519,7 +9521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>851</v>
       </c>
@@ -9537,7 +9539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>853</v>
       </c>
@@ -9553,7 +9555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>855</v>
       </c>
@@ -9571,7 +9573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>856</v>
       </c>
@@ -9593,7 +9595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>858</v>
       </c>
@@ -9613,7 +9615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>860</v>
       </c>
@@ -9631,7 +9633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>862</v>
       </c>
@@ -9649,7 +9651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>864</v>
       </c>
@@ -9665,7 +9667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>866</v>
       </c>
@@ -9683,7 +9685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>868</v>
       </c>
@@ -9701,7 +9703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>869</v>
       </c>
@@ -9721,7 +9723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>871</v>
       </c>
@@ -9737,7 +9739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>873</v>
       </c>
@@ -9759,7 +9761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>875</v>
       </c>
@@ -9777,7 +9779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>877</v>
       </c>
@@ -9793,7 +9795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>879</v>
       </c>
@@ -9822,7 +9824,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -9832,15 +9834,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="50" t="s">
         <v>78</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9863,7 +9865,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>881</v>
       </c>
@@ -9881,7 +9883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>883</v>
       </c>
@@ -9899,7 +9901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>885</v>
       </c>
@@ -9921,7 +9923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>887</v>
       </c>
@@ -9943,7 +9945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>889</v>
       </c>
@@ -9961,7 +9963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>891</v>
       </c>
@@ -9979,7 +9981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>893</v>
       </c>
@@ -9999,7 +10001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>895</v>
       </c>
@@ -10021,7 +10023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>897</v>
       </c>
@@ -10037,7 +10039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>899</v>
       </c>
@@ -10059,7 +10061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>901</v>
       </c>
@@ -10081,7 +10083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>903</v>
       </c>
@@ -10103,7 +10105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>904</v>
       </c>
@@ -10121,7 +10123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>906</v>
       </c>
@@ -10143,7 +10145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>908</v>
       </c>
@@ -10163,7 +10165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>910</v>
       </c>
@@ -10181,7 +10183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>912</v>
       </c>
@@ -10203,7 +10205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>913</v>
       </c>
@@ -10223,7 +10225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>914</v>
       </c>
@@ -10245,7 +10247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>916</v>
       </c>
@@ -10263,7 +10265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>918</v>
       </c>
@@ -10281,7 +10283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>920</v>
       </c>
@@ -10303,7 +10305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>922</v>
       </c>
@@ -10325,7 +10327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>924</v>
       </c>
@@ -10345,7 +10347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>926</v>
       </c>
@@ -10361,7 +10363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>928</v>
       </c>
@@ -10388,7 +10390,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -10398,15 +10400,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
         <v>79</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -10429,7 +10431,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>930</v>
       </c>
@@ -10451,7 +10453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>932</v>
       </c>
@@ -10471,7 +10473,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>934</v>
       </c>
@@ -10489,7 +10491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>936</v>
       </c>
@@ -10511,7 +10513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>938</v>
       </c>
@@ -10529,7 +10531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>940</v>
       </c>
@@ -10547,7 +10549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>942</v>
       </c>
@@ -10567,7 +10569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>944</v>
       </c>
@@ -10583,7 +10585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>946</v>
       </c>
@@ -10605,7 +10607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>948</v>
       </c>
@@ -10623,7 +10625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>950</v>
       </c>
@@ -10641,7 +10643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>952</v>
       </c>
@@ -10659,7 +10661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>954</v>
       </c>
@@ -10675,7 +10677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>956</v>
       </c>
@@ -10693,7 +10695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>958</v>
       </c>
@@ -10711,7 +10713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>959</v>
       </c>
@@ -10729,7 +10731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>961</v>
       </c>
@@ -10747,7 +10749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>963</v>
       </c>
@@ -10765,7 +10767,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>965</v>
       </c>
@@ -10787,7 +10789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>966</v>
       </c>
@@ -10805,7 +10807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>968</v>
       </c>
@@ -10823,7 +10825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>970</v>
       </c>
@@ -10841,7 +10843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>972</v>
       </c>
@@ -10857,7 +10859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>974</v>
       </c>
@@ -10875,7 +10877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>975</v>
       </c>
@@ -10904,18 +10906,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H62"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="39" t="s">
         <v>88</v>
       </c>
@@ -10924,7 +10926,7 @@
       <c r="D1" s="37"/>
       <c r="E1" s="37"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>59</v>
       </c>
@@ -10950,7 +10952,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>63</v>
       </c>
@@ -10973,7 +10975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
         <v>63</v>
       </c>
@@ -10996,7 +10998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
         <v>63</v>
       </c>
@@ -11019,7 +11021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>64</v>
       </c>
@@ -11042,7 +11044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>64</v>
       </c>
@@ -11065,7 +11067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
         <v>64</v>
       </c>
@@ -11088,7 +11090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>65</v>
       </c>
@@ -11111,7 +11113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>65</v>
       </c>
@@ -11134,7 +11136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
         <v>65</v>
       </c>
@@ -11157,7 +11159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>66</v>
       </c>
@@ -11180,7 +11182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>66</v>
       </c>
@@ -11203,7 +11205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
         <v>66</v>
       </c>
@@ -11226,7 +11228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>67</v>
       </c>
@@ -11249,7 +11251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>67</v>
       </c>
@@ -11272,7 +11274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
         <v>67</v>
       </c>
@@ -11295,7 +11297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>68</v>
       </c>
@@ -11318,7 +11320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>68</v>
       </c>
@@ -11341,7 +11343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
         <v>68</v>
       </c>
@@ -11364,7 +11366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>69</v>
       </c>
@@ -11387,7 +11389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>69</v>
       </c>
@@ -11410,7 +11412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
         <v>69</v>
       </c>
@@ -11433,7 +11435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>70</v>
       </c>
@@ -11456,7 +11458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
         <v>70</v>
       </c>
@@ -11479,7 +11481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
         <v>70</v>
       </c>
@@ -11502,7 +11504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>71</v>
       </c>
@@ -11525,7 +11527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>71</v>
       </c>
@@ -11548,7 +11550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
         <v>71</v>
       </c>
@@ -11571,7 +11573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>72</v>
       </c>
@@ -11594,7 +11596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>72</v>
       </c>
@@ -11617,7 +11619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
         <v>72</v>
       </c>
@@ -11640,7 +11642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>73</v>
       </c>
@@ -11663,7 +11665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
         <v>73</v>
       </c>
@@ -11686,7 +11688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
         <v>73</v>
       </c>
@@ -11709,7 +11711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
         <v>74</v>
       </c>
@@ -11732,7 +11734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
         <v>74</v>
       </c>
@@ -11755,7 +11757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
         <v>74</v>
       </c>
@@ -11778,7 +11780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
         <v>75</v>
       </c>
@@ -11801,7 +11803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>75</v>
       </c>
@@ -11824,7 +11826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>75</v>
       </c>
@@ -11847,7 +11849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="s">
         <v>76</v>
       </c>
@@ -11870,7 +11872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
         <v>76</v>
       </c>
@@ -11893,7 +11895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
         <v>76</v>
       </c>
@@ -11916,7 +11918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>77</v>
       </c>
@@ -11939,7 +11941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
         <v>77</v>
       </c>
@@ -11962,7 +11964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
         <v>77</v>
       </c>
@@ -11985,7 +11987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="17" t="s">
         <v>78</v>
       </c>
@@ -12008,7 +12010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
         <v>78</v>
       </c>
@@ -12031,7 +12033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
         <v>78</v>
       </c>
@@ -12054,7 +12056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
         <v>79</v>
       </c>
@@ -12077,7 +12079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
         <v>79</v>
       </c>
@@ -12100,7 +12102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21" t="s">
         <v>79</v>
       </c>
@@ -12123,7 +12125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="17" t="s">
         <v>80</v>
       </c>
@@ -12146,7 +12148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
         <v>80</v>
       </c>
@@ -12169,7 +12171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21" t="s">
         <v>80</v>
       </c>
@@ -12192,7 +12194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
         <v>0</v>
       </c>
@@ -12215,7 +12217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
         <v>0</v>
       </c>
@@ -12238,7 +12240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21" t="s">
         <v>0</v>
       </c>
@@ -12261,7 +12263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="17" t="s">
         <v>81</v>
       </c>
@@ -12284,7 +12286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
         <v>81</v>
       </c>
@@ -12307,7 +12309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="21" t="s">
         <v>81</v>
       </c>
@@ -12341,7 +12343,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -12351,15 +12353,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="51" t="s">
         <v>80</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12382,7 +12384,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>977</v>
       </c>
@@ -12397,14 +12399,14 @@
         <v>3</v>
       </c>
       <c r="F3" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="35">
         <f t="shared" ref="G3:G26" si="0">MAX(0,E3-IF(F3="",0,F3))</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>979</v>
       </c>
@@ -12426,7 +12428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>981</v>
       </c>
@@ -12444,7 +12446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>983</v>
       </c>
@@ -12466,7 +12468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>985</v>
       </c>
@@ -12484,7 +12486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>987</v>
       </c>
@@ -12502,7 +12504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>989</v>
       </c>
@@ -12522,7 +12524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>991</v>
       </c>
@@ -12540,7 +12542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>993</v>
       </c>
@@ -12562,7 +12564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>994</v>
       </c>
@@ -12578,7 +12580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>996</v>
       </c>
@@ -12596,7 +12598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>998</v>
       </c>
@@ -12618,7 +12620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>1000</v>
       </c>
@@ -12636,7 +12638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>1002</v>
       </c>
@@ -12658,7 +12660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>1003</v>
       </c>
@@ -12678,7 +12680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>1005</v>
       </c>
@@ -12694,7 +12696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>1007</v>
       </c>
@@ -12716,7 +12718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>1009</v>
       </c>
@@ -12734,7 +12736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>1011</v>
       </c>
@@ -12756,7 +12758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>1013</v>
       </c>
@@ -12776,7 +12778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>1015</v>
       </c>
@@ -12796,7 +12798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>1017</v>
       </c>
@@ -12818,7 +12820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>1019</v>
       </c>
@@ -12838,7 +12840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>1021</v>
       </c>
@@ -12867,7 +12869,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -12877,7 +12879,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
@@ -12885,7 +12887,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12908,7 +12910,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
@@ -12926,7 +12928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>11</v>
       </c>
@@ -12944,7 +12946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>13</v>
       </c>
@@ -12966,7 +12968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>15</v>
       </c>
@@ -12988,7 +12990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>17</v>
       </c>
@@ -13010,7 +13012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>19</v>
       </c>
@@ -13028,7 +13030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>21</v>
       </c>
@@ -13050,7 +13052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>23</v>
       </c>
@@ -13068,7 +13070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>25</v>
       </c>
@@ -13088,7 +13090,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>27</v>
       </c>
@@ -13106,7 +13108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -13124,7 +13126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>30</v>
       </c>
@@ -13140,7 +13142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>32</v>
       </c>
@@ -13162,7 +13164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>34</v>
       </c>
@@ -13184,7 +13186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>36</v>
       </c>
@@ -13202,7 +13204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>38</v>
       </c>
@@ -13220,7 +13222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>40</v>
       </c>
@@ -13240,7 +13242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>42</v>
       </c>
@@ -13262,7 +13264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>44</v>
       </c>
@@ -13280,7 +13282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>46</v>
       </c>
@@ -13298,7 +13300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>48</v>
       </c>
@@ -13320,7 +13322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>50</v>
       </c>
@@ -13340,7 +13342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>52</v>
       </c>
@@ -13358,7 +13360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>54</v>
       </c>
@@ -13374,7 +13376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>56</v>
       </c>
@@ -13401,7 +13403,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -13411,15 +13413,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="36" t="s">
         <v>81</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13442,7 +13444,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>1023</v>
       </c>
@@ -13464,7 +13466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>1025</v>
       </c>
@@ -13482,7 +13484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>1027</v>
       </c>
@@ -13504,7 +13506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>1028</v>
       </c>
@@ -13526,7 +13528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>1030</v>
       </c>
@@ -13544,7 +13546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>1032</v>
       </c>
@@ -13566,7 +13568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>1034</v>
       </c>
@@ -13582,7 +13584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>1036</v>
       </c>
@@ -13600,7 +13602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>1038</v>
       </c>
@@ -13618,7 +13620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>1040</v>
       </c>
@@ -13634,7 +13636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>1042</v>
       </c>
@@ -13654,7 +13656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>1044</v>
       </c>
@@ -13672,7 +13674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>1046</v>
       </c>
@@ -13690,7 +13692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>1048</v>
       </c>
@@ -13708,7 +13710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>1050</v>
       </c>
@@ -13726,7 +13728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>1052</v>
       </c>
@@ -13744,7 +13746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>1054</v>
       </c>
@@ -13762,7 +13764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>1056</v>
       </c>
@@ -13780,7 +13782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>1058</v>
       </c>
@@ -13800,7 +13802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>1060</v>
       </c>
@@ -13818,7 +13820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>1062</v>
       </c>
@@ -13836,7 +13838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>1063</v>
       </c>
@@ -13854,7 +13856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>1065</v>
       </c>
@@ -13870,7 +13872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>1067</v>
       </c>
@@ -13888,7 +13890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>1069</v>
       </c>
@@ -13917,7 +13919,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -13927,7 +13929,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
         <v>82</v>
       </c>
@@ -13935,7 +13937,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13958,7 +13960,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>1071</v>
       </c>
@@ -13976,7 +13978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>1073</v>
       </c>
@@ -13994,7 +13996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>1075</v>
       </c>
@@ -14016,7 +14018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>1077</v>
       </c>
@@ -14038,7 +14040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>1079</v>
       </c>
@@ -14060,7 +14062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>1081</v>
       </c>
@@ -14078,7 +14080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>1083</v>
       </c>
@@ -14100,7 +14102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>1085</v>
       </c>
@@ -14122,7 +14124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>1087</v>
       </c>
@@ -14144,7 +14146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>1089</v>
       </c>
@@ -14166,7 +14168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>1091</v>
       </c>
@@ -14184,7 +14186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>1093</v>
       </c>
@@ -14202,7 +14204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>1095</v>
       </c>
@@ -14224,7 +14226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>1097</v>
       </c>
@@ -14246,7 +14248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>1099</v>
       </c>
@@ -14268,7 +14270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>1101</v>
       </c>
@@ -14290,7 +14292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>1103</v>
       </c>
@@ -14312,7 +14314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>1105</v>
       </c>
@@ -14334,7 +14336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>1107</v>
       </c>
@@ -14356,7 +14358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>1109</v>
       </c>
@@ -14374,7 +14376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>1111</v>
       </c>
@@ -14396,7 +14398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>1113</v>
       </c>
@@ -14414,7 +14416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>1115</v>
       </c>
@@ -14432,7 +14434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>1117</v>
       </c>
@@ -14454,7 +14456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>1119</v>
       </c>
@@ -14476,7 +14478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>1121</v>
       </c>
@@ -14494,7 +14496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>1123</v>
       </c>
@@ -14516,7 +14518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>1125</v>
       </c>
@@ -14538,7 +14540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>1127</v>
       </c>
@@ -14560,7 +14562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>1129</v>
       </c>
@@ -14582,7 +14584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>1131</v>
       </c>
@@ -14604,7 +14606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>1133</v>
       </c>
@@ -14633,7 +14635,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -14643,7 +14645,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
         <v>83</v>
       </c>
@@ -14651,7 +14653,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -14674,7 +14676,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>1135</v>
       </c>
@@ -14692,7 +14694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>1137</v>
       </c>
@@ -14714,7 +14716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>1139</v>
       </c>
@@ -14732,7 +14734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>1141</v>
       </c>
@@ -14754,7 +14756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>1143</v>
       </c>
@@ -14776,7 +14778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>1145</v>
       </c>
@@ -14796,7 +14798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>1147</v>
       </c>
@@ -14816,7 +14818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>1149</v>
       </c>
@@ -14834,7 +14836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>1151</v>
       </c>
@@ -14852,7 +14854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>1153</v>
       </c>
@@ -14870,7 +14872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>1155</v>
       </c>
@@ -14888,7 +14890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>1157</v>
       </c>
@@ -14906,7 +14908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>1159</v>
       </c>
@@ -14926,7 +14928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>1161</v>
       </c>
@@ -14944,7 +14946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>1163</v>
       </c>
@@ -14964,7 +14966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>1165</v>
       </c>
@@ -14982,7 +14984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>1167</v>
       </c>
@@ -15002,7 +15004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>1169</v>
       </c>
@@ -15024,7 +15026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>1171</v>
       </c>
@@ -15046,7 +15048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>1173</v>
       </c>
@@ -15064,7 +15066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>1175</v>
       </c>
@@ -15082,7 +15084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>1177</v>
       </c>
@@ -15104,7 +15106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>1179</v>
       </c>
@@ -15122,7 +15124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>1181</v>
       </c>
@@ -15140,7 +15142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>1183</v>
       </c>
@@ -15160,7 +15162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>1185</v>
       </c>
@@ -15182,7 +15184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>1187</v>
       </c>
@@ -15200,7 +15202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>1189</v>
       </c>
@@ -15218,7 +15220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>1191</v>
       </c>
@@ -15236,7 +15238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>1193</v>
       </c>
@@ -15254,7 +15256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>1195</v>
       </c>
@@ -15272,7 +15274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>1197</v>
       </c>
@@ -15294,7 +15296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>1199</v>
       </c>
@@ -15312,7 +15314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
         <v>1201</v>
       </c>
@@ -15330,7 +15332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>1203</v>
       </c>
@@ -15348,7 +15350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
         <v>1205</v>
       </c>
@@ -15366,7 +15368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>1207</v>
       </c>
@@ -15384,7 +15386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
         <v>1209</v>
       </c>
@@ -15402,7 +15404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>1211</v>
       </c>
@@ -15420,7 +15422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
         <v>1213</v>
       </c>
@@ -15442,7 +15444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>1215</v>
       </c>
@@ -15460,7 +15462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>1217</v>
       </c>
@@ -15478,7 +15480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>1219</v>
       </c>
@@ -15496,7 +15498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>1221</v>
       </c>
@@ -15514,7 +15516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>1223</v>
       </c>
@@ -15532,7 +15534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
         <v>1225</v>
       </c>
@@ -15550,7 +15552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>1227</v>
       </c>
@@ -15568,7 +15570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
         <v>1229</v>
       </c>
@@ -15586,7 +15588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>1231</v>
       </c>
@@ -15604,7 +15606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="15" t="s">
         <v>1233</v>
       </c>
@@ -15622,7 +15624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
         <v>1235</v>
       </c>
@@ -15640,7 +15642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="15" t="s">
         <v>1237</v>
       </c>
@@ -15658,7 +15660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>1239</v>
       </c>
@@ -15676,7 +15678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="15" t="s">
         <v>1241</v>
       </c>
@@ -15694,7 +15696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>1243</v>
       </c>
@@ -15712,7 +15714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>1245</v>
       </c>
@@ -15730,7 +15732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
         <v>1247</v>
       </c>
@@ -15748,7 +15750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
         <v>1249</v>
       </c>
@@ -15766,7 +15768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
         <v>1251</v>
       </c>
@@ -15784,7 +15786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
         <v>1253</v>
       </c>
@@ -15802,7 +15804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
         <v>1255</v>
       </c>
@@ -15820,7 +15822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
         <v>1257</v>
       </c>
@@ -15838,7 +15840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
         <v>1259</v>
       </c>
@@ -15856,7 +15858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="15" t="s">
         <v>1261</v>
       </c>
@@ -15874,7 +15876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
         <v>1263</v>
       </c>
@@ -15892,7 +15894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
         <v>1265</v>
       </c>
@@ -15921,18 +15923,18 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="55" t="s">
         <v>84</v>
       </c>
@@ -15940,7 +15942,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -15963,7 +15965,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>1267</v>
       </c>
@@ -15985,7 +15987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>1269</v>
       </c>
@@ -16005,7 +16007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>1271</v>
       </c>
@@ -16027,7 +16029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>1273</v>
       </c>
@@ -16049,7 +16051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>1275</v>
       </c>
@@ -16071,7 +16073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>1277</v>
       </c>
@@ -16093,7 +16095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>1279</v>
       </c>
@@ -16115,7 +16117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>1281</v>
       </c>
@@ -16135,7 +16137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>1283</v>
       </c>
@@ -16166,7 +16168,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -16176,7 +16178,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="40" t="s">
         <v>63</v>
       </c>
@@ -16184,7 +16186,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -16207,7 +16209,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>152</v>
       </c>
@@ -16229,7 +16231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>154</v>
       </c>
@@ -16251,7 +16253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>156</v>
       </c>
@@ -16269,7 +16271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>158</v>
       </c>
@@ -16287,7 +16289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>160</v>
       </c>
@@ -16309,7 +16311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>161</v>
       </c>
@@ -16331,7 +16333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>163</v>
       </c>
@@ -16353,7 +16355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>165</v>
       </c>
@@ -16371,7 +16373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>167</v>
       </c>
@@ -16389,7 +16391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>169</v>
       </c>
@@ -16411,7 +16413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>171</v>
       </c>
@@ -16431,7 +16433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>173</v>
       </c>
@@ -16449,7 +16451,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>175</v>
       </c>
@@ -16467,7 +16469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>177</v>
       </c>
@@ -16485,7 +16487,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>179</v>
       </c>
@@ -16507,7 +16509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>181</v>
       </c>
@@ -16523,7 +16525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>183</v>
       </c>
@@ -16541,7 +16543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>185</v>
       </c>
@@ -16563,7 +16565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>186</v>
       </c>
@@ -16581,7 +16583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>188</v>
       </c>
@@ -16599,7 +16601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>189</v>
       </c>
@@ -16621,7 +16623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>191</v>
       </c>
@@ -16637,7 +16639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>193</v>
       </c>
@@ -16659,7 +16661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>195</v>
       </c>
@@ -16681,7 +16683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>197</v>
       </c>
@@ -16699,7 +16701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>199</v>
       </c>
@@ -16717,7 +16719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>201</v>
       </c>
@@ -16744,7 +16746,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -16754,7 +16756,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="41" t="s">
         <v>64</v>
       </c>
@@ -16762,7 +16764,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -16785,7 +16787,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>203</v>
       </c>
@@ -16803,7 +16805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>205</v>
       </c>
@@ -16823,7 +16825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>207</v>
       </c>
@@ -16841,7 +16843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>208</v>
       </c>
@@ -16863,7 +16865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>210</v>
       </c>
@@ -16881,7 +16883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>212</v>
       </c>
@@ -16897,7 +16899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>214</v>
       </c>
@@ -16913,7 +16915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>216</v>
       </c>
@@ -16931,7 +16933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>218</v>
       </c>
@@ -16951,7 +16953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>220</v>
       </c>
@@ -16973,7 +16975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>222</v>
       </c>
@@ -16991,7 +16993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>224</v>
       </c>
@@ -17013,7 +17015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>226</v>
       </c>
@@ -17033,7 +17035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>228</v>
       </c>
@@ -17055,7 +17057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>230</v>
       </c>
@@ -17077,7 +17079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>232</v>
       </c>
@@ -17099,7 +17101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>233</v>
       </c>
@@ -17119,7 +17121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>235</v>
       </c>
@@ -17141,7 +17143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>237</v>
       </c>
@@ -17159,7 +17161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>239</v>
       </c>
@@ -17177,7 +17179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>241</v>
       </c>
@@ -17195,7 +17197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>243</v>
       </c>
@@ -17211,7 +17213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>245</v>
       </c>
@@ -17233,7 +17235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>246</v>
       </c>
@@ -17251,7 +17253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>248</v>
       </c>
@@ -17269,7 +17271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>250</v>
       </c>
@@ -17296,7 +17298,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -17306,7 +17308,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="41" t="s">
         <v>65</v>
       </c>
@@ -17314,7 +17316,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -17337,7 +17339,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>252</v>
       </c>
@@ -17355,7 +17357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>254</v>
       </c>
@@ -17377,7 +17379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>256</v>
       </c>
@@ -17395,7 +17397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>257</v>
       </c>
@@ -17417,7 +17419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>259</v>
       </c>
@@ -17439,7 +17441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>261</v>
       </c>
@@ -17459,7 +17461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>263</v>
       </c>
@@ -17475,7 +17477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>265</v>
       </c>
@@ -17493,7 +17495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>267</v>
       </c>
@@ -17515,7 +17517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>269</v>
       </c>
@@ -17537,7 +17539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>271</v>
       </c>
@@ -17555,7 +17557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>273</v>
       </c>
@@ -17577,7 +17579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>275</v>
       </c>
@@ -17597,7 +17599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>277</v>
       </c>
@@ -17615,7 +17617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>279</v>
       </c>
@@ -17633,7 +17635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>281</v>
       </c>
@@ -17649,7 +17651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>283</v>
       </c>
@@ -17669,7 +17671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>285</v>
       </c>
@@ -17691,7 +17693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>287</v>
       </c>
@@ -17713,7 +17715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>289</v>
       </c>
@@ -17735,7 +17737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>291</v>
       </c>
@@ -17753,7 +17755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>292</v>
       </c>
@@ -17771,7 +17773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>294</v>
       </c>
@@ -17789,7 +17791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>295</v>
       </c>
@@ -17807,7 +17809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>297</v>
       </c>
@@ -17836,7 +17838,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -17846,7 +17848,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
         <v>66</v>
       </c>
@@ -17854,7 +17856,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -17877,7 +17879,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>299</v>
       </c>
@@ -17895,7 +17897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>301</v>
       </c>
@@ -17917,7 +17919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>303</v>
       </c>
@@ -17935,7 +17937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>305</v>
       </c>
@@ -17957,7 +17959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>307</v>
       </c>
@@ -17979,7 +17981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>309</v>
       </c>
@@ -18001,7 +18003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>311</v>
       </c>
@@ -18023,7 +18025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>313</v>
       </c>
@@ -18039,7 +18041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>315</v>
       </c>
@@ -18061,7 +18063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>317</v>
       </c>
@@ -18079,7 +18081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>319</v>
       </c>
@@ -18097,7 +18099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>321</v>
       </c>
@@ -18115,7 +18117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>323</v>
       </c>
@@ -18133,7 +18135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>325</v>
       </c>
@@ -18155,7 +18157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>327</v>
       </c>
@@ -18173,7 +18175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>328</v>
       </c>
@@ -18191,7 +18193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>330</v>
       </c>
@@ -18207,7 +18209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>332</v>
       </c>
@@ -18229,7 +18231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>333</v>
       </c>
@@ -18247,7 +18249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>334</v>
       </c>
@@ -18269,7 +18271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>336</v>
       </c>
@@ -18287,7 +18289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>338</v>
       </c>
@@ -18307,7 +18309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>340</v>
       </c>
@@ -18329,7 +18331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>342</v>
       </c>
@@ -18347,7 +18349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>344</v>
       </c>
@@ -18374,7 +18376,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -18384,7 +18386,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
         <v>67</v>
       </c>
@@ -18392,7 +18394,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -18415,7 +18417,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>346</v>
       </c>
@@ -18433,7 +18435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>348</v>
       </c>
@@ -18455,7 +18457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>350</v>
       </c>
@@ -18473,7 +18475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>351</v>
       </c>
@@ -18491,7 +18493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>353</v>
       </c>
@@ -18513,7 +18515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>355</v>
       </c>
@@ -18529,7 +18531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>357</v>
       </c>
@@ -18551,7 +18553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>359</v>
       </c>
@@ -18567,7 +18569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>361</v>
       </c>
@@ -18585,7 +18587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>363</v>
       </c>
@@ -18607,7 +18609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>365</v>
       </c>
@@ -18623,7 +18625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>367</v>
       </c>
@@ -18645,7 +18647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>369</v>
       </c>
@@ -18663,7 +18665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>371</v>
       </c>
@@ -18683,7 +18685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>373</v>
       </c>
@@ -18701,7 +18703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>375</v>
       </c>
@@ -18719,7 +18721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>376</v>
       </c>
@@ -18737,7 +18739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>378</v>
       </c>
@@ -18759,7 +18761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>380</v>
       </c>
@@ -18781,7 +18783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>382</v>
       </c>
@@ -18801,7 +18803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>384</v>
       </c>
@@ -18823,7 +18825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>386</v>
       </c>
@@ -18843,7 +18845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>388</v>
       </c>
@@ -18861,7 +18863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>390</v>
       </c>
@@ -18879,7 +18881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>392</v>
       </c>
@@ -18899,7 +18901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>394</v>
       </c>
@@ -18917,7 +18919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>396</v>
       </c>
@@ -18935,7 +18937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>398</v>
       </c>
@@ -18962,7 +18964,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -18972,15 +18974,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="36" t="s">
         <v>68</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -19003,7 +19005,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>400</v>
       </c>
@@ -19025,7 +19027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>402</v>
       </c>
@@ -19043,7 +19045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>404</v>
       </c>
@@ -19061,7 +19063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>405</v>
       </c>
@@ -19079,7 +19081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>407</v>
       </c>
@@ -19097,7 +19099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>408</v>
       </c>
@@ -19115,7 +19117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>410</v>
       </c>
@@ -19133,7 +19135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>412</v>
       </c>
@@ -19153,7 +19155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>414</v>
       </c>
@@ -19173,7 +19175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>416</v>
       </c>
@@ -19191,7 +19193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>418</v>
       </c>
@@ -19213,7 +19215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>420</v>
       </c>
@@ -19231,7 +19233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>422</v>
       </c>
@@ -19249,7 +19251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>424</v>
       </c>
@@ -19267,7 +19269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>426</v>
       </c>
@@ -19285,7 +19287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>428</v>
       </c>
@@ -19305,7 +19307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>430</v>
       </c>
@@ -19327,7 +19329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>432</v>
       </c>
@@ -19347,7 +19349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>434</v>
       </c>
@@ -19365,7 +19367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>436</v>
       </c>
@@ -19383,7 +19385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>437</v>
       </c>
@@ -19401,7 +19403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>439</v>
       </c>
@@ -19423,7 +19425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>441</v>
       </c>
@@ -19443,7 +19445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>443</v>
       </c>
@@ -19461,7 +19463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>445</v>
       </c>
@@ -19479,7 +19481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>447</v>
       </c>
@@ -19506,7 +19508,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -19516,15 +19518,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="44" t="s">
         <v>69</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -19547,7 +19549,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>449</v>
       </c>
@@ -19565,7 +19567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>451</v>
       </c>
@@ -19583,7 +19585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>453</v>
       </c>
@@ -19605,7 +19607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>454</v>
       </c>
@@ -19623,7 +19625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>456</v>
       </c>
@@ -19641,7 +19643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>458</v>
       </c>
@@ -19659,7 +19661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>460</v>
       </c>
@@ -19681,7 +19683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>462</v>
       </c>
@@ -19703,7 +19705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>464</v>
       </c>
@@ -19723,7 +19725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>466</v>
       </c>
@@ -19745,7 +19747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>468</v>
       </c>
@@ -19763,7 +19765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>469</v>
       </c>
@@ -19781,7 +19783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>471</v>
       </c>
@@ -19801,7 +19803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>473</v>
       </c>
@@ -19819,7 +19821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>475</v>
       </c>
@@ -19841,7 +19843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>477</v>
       </c>
@@ -19859,7 +19861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>478</v>
       </c>
@@ -19881,7 +19883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>480</v>
       </c>
@@ -19899,7 +19901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>482</v>
       </c>
@@ -19921,7 +19923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>484</v>
       </c>
@@ -19939,7 +19941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>486</v>
       </c>
@@ -19957,7 +19959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>488</v>
       </c>
@@ -19979,7 +19981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>489</v>
       </c>
@@ -19997,7 +19999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>491</v>
       </c>

--- a/Liga 2021-22/cromos_laliga.xlsx
+++ b/Liga 2021-22/cromos_laliga.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuari\Documents\Cromos\Liga 2021-22\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41AE1BD-DBD5-4171-AA6A-B92EF4B74B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7858416D-C45E-4D16-804A-295F146F39A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -4391,7 +4391,7 @@
     <xf numFmtId="0" fontId="3" fillId="37" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -4413,6 +4413,9 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4423,9 +4426,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4843,11 +4843,11 @@
       </c>
       <c r="F4" s="28">
         <f>SUM('ATHLETIC CLUB'!F3:F28)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="33">
         <f>SUM('ATHLETIC CLUB'!G3:G28)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -4927,11 +4927,11 @@
       </c>
       <c r="F7" s="28">
         <f>SUM('REAL BETIS'!F3:F30)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="33">
         <f>SUM('REAL BETIS'!G3:G30)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -4983,11 +4983,11 @@
       </c>
       <c r="F9" s="28">
         <f>SUM('RC CELTA'!F3:F26)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" s="33">
         <f>SUM('RC CELTA'!G3:G26)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -5488,11 +5488,11 @@
       </c>
       <c r="F27" s="30">
         <f t="shared" si="0"/>
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G27" s="34">
         <f t="shared" si="0"/>
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -5529,7 +5529,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>70</v>
       </c>
       <c r="B1" s="37"/>
@@ -6077,7 +6077,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="47" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="37"/>
@@ -6605,7 +6605,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="48" t="s">
         <v>72</v>
       </c>
       <c r="B1" s="37"/>
@@ -7691,7 +7691,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="36" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="37"/>
@@ -10401,7 +10401,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="47" t="s">
         <v>79</v>
       </c>
       <c r="B1" s="37"/>
@@ -13414,7 +13414,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="44" t="s">
         <v>81</v>
       </c>
       <c r="B1" s="37"/>
@@ -17136,11 +17136,11 @@
         <v>3</v>
       </c>
       <c r="F20" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -18546,11 +18546,11 @@
         <v>3</v>
       </c>
       <c r="F9" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="35">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -18975,7 +18975,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="44" t="s">
         <v>68</v>
       </c>
       <c r="B1" s="37"/>
@@ -19519,7 +19519,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="45" t="s">
         <v>69</v>
       </c>
       <c r="B1" s="37"/>
@@ -19876,11 +19876,11 @@
         <v>2</v>
       </c>
       <c r="F19" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
